--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/ARIZONA_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/ARIZONA_2013.xlsx
@@ -2454,7 +2454,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C117">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C259">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C638">
@@ -12768,7 +12768,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C690">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C691">
@@ -17808,7 +17808,7 @@
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C970">
@@ -19104,7 +19104,7 @@
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1042">
